--- a/artfynd/A 4736-2020 artfynd.xlsx
+++ b/artfynd/A 4736-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 4736-2020 artfynd.xlsx
+++ b/artfynd/A 4736-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1170,14 +1170,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>82236744</v>
+        <v>96173612</v>
       </c>
       <c r="B6" t="n">
         <v>96334</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1203,28 +1203,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Smedjehult, Sm</t>
+          <t>Björkhaga, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>508261.866464677</v>
+        <v>508339.4887534893</v>
       </c>
       <c r="R6" t="n">
-        <v>6275466.090244456</v>
+        <v>6275515.750947688</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1248,7 +1244,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2020-02-13</t>
+          <t>2021-09-18</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1258,7 +1254,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2020-02-13</t>
+          <t>2021-09-18</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -1267,7 +1263,7 @@
         </is>
       </c>
       <c r="AD6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
@@ -1276,34 +1272,34 @@
       <c r="AG6" t="b">
         <v>0</v>
       </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>hygge</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Birgitta Warodell</t>
+          <t>Per Darell</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Birgitta Warodell</t>
+          <t>Per Darell, Johan Blomby</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>96173612</v>
+        <v>96173597</v>
       </c>
       <c r="B7" t="n">
         <v>96334</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1329,8 +1325,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
@@ -1340,10 +1344,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>508339.4887534893</v>
+        <v>508270.6825541615</v>
       </c>
       <c r="R7" t="n">
-        <v>6275515.750947688</v>
+        <v>6275467.757819189</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1388,8 +1392,13 @@
           <t>00:00</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>1 överblommad</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
@@ -1400,7 +1409,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>hygge</t>
+          <t>barrskog</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1415,141 +1424,6 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>96173597</v>
-      </c>
-      <c r="B8" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Björkhaga, Sm</t>
-        </is>
-      </c>
-      <c r="Q8" t="n">
-        <v>508270.6825541615</v>
-      </c>
-      <c r="R8" t="n">
-        <v>6275467.757819189</v>
-      </c>
-      <c r="S8" t="n">
-        <v>25</v>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Kronoberg</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Tingsryd</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>Linneryd</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2021-09-18</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>2021-09-18</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>1 överblommad</t>
-        </is>
-      </c>
-      <c r="AD8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF8" t="inlineStr"/>
-      <c r="AG8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>barrskog</t>
-        </is>
-      </c>
-      <c r="AT8" t="inlineStr"/>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>Per Darell</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>Per Darell, Johan Blomby</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
